--- a/output/pdf_financials_xlsx/VUL.xlsx
+++ b/output/pdf_financials_xlsx/VUL.xlsx
@@ -5647,10 +5647,10 @@
         <v>2.122888</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.046574</v>
+        <v>2.169392</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.069864</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
@@ -7062,19 +7062,19 @@
         <v>-0.112338</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>-0.161647</v>
+        <v>-0.972343</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>-0.023281</v>
+        <v>-0.389868</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.01265</v>
+        <v>-0.761486</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.034849</v>
+        <v>-0.5683049999999999</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0.040398</v>
+        <v>-0.327106</v>
       </c>
     </row>
     <row r="119">
@@ -18668,7 +18668,11 @@
           <t>Share based payment reserve (Note 12 (d)) 2,378,069</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -22708,7 +22712,11 @@
           <t>Exploration and evaluation expenditures (Note 7)</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -27606,7 +27614,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VUL.xlsx
+++ b/output/pdf_financials_xlsx/VUL.xlsx
@@ -1018,31 +1018,31 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003467</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.026193</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.035734</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.048304</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.050682</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.037449</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.017897</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.010126</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000748</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1053,16 +1053,16 @@
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.09435200000000001</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.251514</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.275456</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.12715</v>
       </c>
     </row>
     <row r="13">
@@ -1943,31 +1943,31 @@
         <v>-1.038219</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.21827</v>
+        <v>-0.221737</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.073751</v>
+        <v>0.047558</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.797519</v>
+        <v>-1.833253</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.432788</v>
+        <v>-2.481092</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.821741</v>
+        <v>-1.872423</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.18571</v>
+        <v>-1.223159</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.761296</v>
+        <v>-1.779193</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.809182</v>
+        <v>-0.819308</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.71948</v>
+        <v>-1.720228</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.465043</v>
@@ -1978,16 +1978,16 @@
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.755252</v>
+        <v>-2.849604</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.77488</v>
+        <v>-1.026394</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.494725</v>
+        <v>-1.770181</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.573435</v>
+        <v>-2.700585</v>
       </c>
     </row>
     <row r="28">
@@ -2057,31 +2057,31 @@
         <v>-1.038219</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.21827</v>
+        <v>-0.221737</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.073751</v>
+        <v>0.047558</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.797519</v>
+        <v>-1.833253</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.432788</v>
+        <v>-2.481092</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.821741</v>
+        <v>-1.872423</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.18571</v>
+        <v>-1.223159</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.736655</v>
+        <v>-1.754552</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.7907650000000001</v>
+        <v>-0.800891</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.707049</v>
+        <v>-1.707797</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.456158</v>
@@ -2092,16 +2092,16 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.749418</v>
+        <v>-2.84377</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.768445</v>
+        <v>-1.019959</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.485401</v>
+        <v>-1.760857</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.565978</v>
+        <v>-2.693128</v>
       </c>
     </row>
     <row r="30">
@@ -2114,13 +2114,13 @@
         <v>-6071.811217030236</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-85.27237779722465</v>
+        <v>-86.62684398049755</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>14.01595992345014</v>
+        <v>9.038128595401307</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-5030.276487378967</v>
+        <v>-5130.276487378967</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>2.747212</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.183306</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.254492</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.034678</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.322672</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>5.449161</v>
@@ -2464,16 +2464,16 @@
         <v>2.747212</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.183306</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.254492</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.034678</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.322672</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>5.449161</v>
@@ -3124,16 +3124,16 @@
         <v>0.110866</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.21275</v>
+        <v>0.029444</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.345454</v>
+        <v>0.090962</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.04737</v>
+        <v>0.012692</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.332563</v>
+        <v>0.009891</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.009582</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -35506,7 +35506,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -38034,7 +38034,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -40872,7 +40872,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -43624,7 +43624,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -45542,7 +45542,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">

--- a/output/pdf_financials_xlsx/VUL.xlsx
+++ b/output/pdf_financials_xlsx/VUL.xlsx
@@ -768,16 +768,16 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="8">
@@ -945,10 +945,10 @@
         <v>0.499518</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="11">
@@ -1273,7 +1273,7 @@
         <v>-1.71948</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.465043</v>
+        <v>-0.456377</v>
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
@@ -1306,16 +1306,16 @@
         <v>-0.011307</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.488308</v>
+        <v>0.476876</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.061902</v>
+        <v>0.067929</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.76575</v>
+        <v>-0.765787</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.096161</v>
+        <v>-0.096161</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1330,7 +1330,7 @@
         <v>-0</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.008666</v>
       </c>
       <c r="M17" s="1" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>-1.720228</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.465043</v>
+        <v>-0.456377</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>-1.707797</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.456158</v>
+        <v>-0.447492</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2196,13 +2196,13 @@
         <v>-5.180281302973381</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>662.1035646974278</v>
+        <v>646.6027579287061</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-3.443746630772748</v>
+        <v>-3.779042113045815</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-31.4762322076564</v>
+        <v>-31.47775309644737</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-5.278522029201736</v>
@@ -2220,7 +2220,7 @@
         <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.898868698466399</v>
       </c>
       <c r="M31" s="1" t="inlineStr">
         <is>
@@ -6644,31 +6644,31 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.015668</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001308</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.014073</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.163141</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.010089</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001607</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004634</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002756</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.211457</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -7941,31 +7941,31 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.015668</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001308</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.014073</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.163141</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.010089</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001607</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004634</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002756</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
@@ -7996,31 +7996,31 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.00108</v>
+        <v>-1.016748</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.009745999999999999</v>
+        <v>-0.011054</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.442402</v>
+        <v>-0.456475</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.6895829999999999</v>
+        <v>-0.852724</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.877332</v>
+        <v>-0.887421</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.785536</v>
+        <v>-0.787143</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-0.674884</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.610554</v>
+        <v>-0.615188</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-0.603602</v>
+        <v>-0.606358</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-0.613206</v>
@@ -28458,7 +28458,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -31206,7 +31210,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -33988,7 +33996,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E278" s="5" t="n">
         <v>-0.015668</v>
       </c>
@@ -34556,7 +34568,11 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E284" s="5" t="n">
         <v>-0.211457</v>
       </c>
@@ -35126,7 +35142,11 @@
           <t>Directors' fees</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -35198,10 +35218,10 @@
         </is>
       </c>
       <c r="S290" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="T290" s="5" t="n">
-        <v>-0.047</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="291">
@@ -36604,7 +36624,11 @@
           <t>Director's fees</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -36666,13 +36690,13 @@
         </is>
       </c>
       <c r="Q306" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="R306" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="S306" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -38792,7 +38816,11 @@
           <t>Deferred income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -41534,7 +41562,11 @@
           <t>Deferred income tax recovery (Note 9 (b))</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -42192,7 +42224,11 @@
           <t>Deferred income tax recovery (Note 10 (b))</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -44488,7 +44524,11 @@
           <t>Deferred income tax recovery (Note 11 (b))</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -46498,7 +46538,11 @@
           <t>Deferred income tax recovery (expense) (Note 11 (b))</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -48030,7 +48074,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -48406,7 +48454,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
